--- a/assets/translations/Arabic.ModernStandard.ar-.xlsx
+++ b/assets/translations/Arabic.ModernStandard.ar-.xlsx
@@ -8,7 +8,7 @@
       <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="/Users/zauner/Documents/Arbeit/12-TUM/Repos_Misc/2024-04_Ladenburg_Roundtable/LCS/assets/translations/"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{BA3762C8-1463-6C4C-AC80-CEDC3EF7320B}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
+  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{1EC93C46-C047-6843-84E5-1DAF7485922D}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
   <bookViews>
     <workbookView xWindow="1180" yWindow="680" windowWidth="33380" windowHeight="21660" activeTab="3" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
   </bookViews>
@@ -645,7 +645,7 @@
     <t>رقم</t>
   </si>
   <si>
-    <t>البيانات التوافقيّة</t>
+    <t>بيانات توافقيّة</t>
   </si>
 </sst>
 </file>
